--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260626.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260626.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>26.64%</t>
+          <t>25.97%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.73%</t>
+          <t>8.52%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.77%</t>
+          <t>7.67%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.31%</t>
+          <t>7.03%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.43%</t>
+          <t>5.55%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.20%</t>
+          <t>3.29%</t>
         </is>
       </c>
     </row>
@@ -748,73 +748,73 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>3.19%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>DUK US</t>
+          <t>NOW US</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>杜克能源公司</t>
+          <t>ServiceNow Inc</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>52,335</t>
+          <t>68,880</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>3.02%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>DUK US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>杜克能源公司</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>22,895</t>
+          <t>52,335</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>3.00%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>NOW US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>ServiceNow Inc</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>68,880</t>
+          <t>22,895</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>2.69%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.26%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.24%</t>
         </is>
       </c>
     </row>
@@ -880,24 +880,24 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>HPE US</t>
+          <t>D US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>慧與</t>
+          <t>道明尼能源公司</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>89,195</t>
+          <t>59,155</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -909,110 +909,110 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>D US</t>
+          <t>HPE US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>道明尼能源公司</t>
+          <t>慧與</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>59,155</t>
+          <t>89,195</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.74%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>22,600</t>
+          <t>124,043,363</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.73%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>9,300</t>
+          <t>22,600</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>30,798</t>
+          <t>9,300</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.62%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>13,611</t>
+          <t>30,798</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.59%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
@@ -1056,46 +1056,46 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>11,196</t>
+          <t>13,611</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>89,993,363</t>
+          <t>24,738</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1107,22 +1107,22 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>24,738</t>
+          <t>11,196</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
@@ -1166,51 +1166,51 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>22,867</t>
+          <t>18,521</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>18,521</t>
+          <t>22,867</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
